--- a/output_data/task3_data_faireness_analysis.xlsx
+++ b/output_data/task3_data_faireness_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My_projects\Sherif\project2\output_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD5B0133-9DA9-4B69-AD1F-41B8EA1C4E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6433A344-6E87-4813-94D9-FEA0032C340D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{326258D0-99DD-4727-9A96-8B450F138D2C}"/>
   </bookViews>
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">task2_cleaned_data!$A$1:$R$405</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3676" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3678" uniqueCount="144">
   <si>
     <t>checkout_id</t>
   </si>
@@ -454,6 +467,9 @@
   <si>
     <t>count</t>
   </si>
+  <si>
+    <t>Total</t>
+  </si>
 </sst>
 </file>
 
@@ -776,7 +792,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -891,6 +907,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -936,9 +967,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -23507,8 +23539,11 @@
       <c r="F1" t="s">
         <v>142</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>9</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -23526,10 +23561,10 @@
         <f>COUNTIF(task2_cleaned_data!R:R,summary!E2)</f>
         <v>40</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <f>COUNTIF(task2_cleaned_data!J:J,summary!H2)</f>
         <v>87</v>
       </c>
@@ -23549,10 +23584,10 @@
         <f>COUNTIF(task2_cleaned_data!R:R,summary!E3)</f>
         <v>110</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <f>COUNTIF(task2_cleaned_data!J:J,summary!H3)</f>
         <v>68</v>
       </c>
@@ -23572,10 +23607,10 @@
         <f>COUNTIF(task2_cleaned_data!R:R,summary!E4)</f>
         <v>202</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <f>COUNTIF(task2_cleaned_data!J:J,summary!H4)</f>
         <v>101</v>
       </c>
@@ -23595,10 +23630,10 @@
         <f>COUNTIF(task2_cleaned_data!R:R,summary!E5)</f>
         <v>52</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <f>COUNTIF(task2_cleaned_data!J:J,summary!H5)</f>
         <v>34</v>
       </c>
@@ -23611,10 +23646,10 @@
         <f>COUNTIF(task2_cleaned_data!O:O,summary!A6)</f>
         <v>109</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <f>COUNTIF(task2_cleaned_data!J:J,summary!H6)</f>
         <v>114</v>
       </c>
@@ -23627,6 +23662,8 @@
         <f>COUNTIF(task2_cleaned_data!O:O,summary!A7)</f>
         <v>61</v>
       </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -23635,6 +23672,13 @@
       <c r="B8">
         <f>COUNTIF(task2_cleaned_data!O:O,summary!A8)</f>
         <v>5</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I8" s="2">
+        <f>SUM(I2:I7)</f>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -23655,10 +23699,6 @@
         <f>SUM(F2:F5)</f>
         <v>404</v>
       </c>
-      <c r="I11">
-        <f>SUM(I2:I7)</f>
-        <v>404</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
